--- a/VKTX.xlsx
+++ b/VKTX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffe\Documents\GitHub\martinshkreli-models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6944C6CF-5CDC-4DEB-BEF3-728FF9E35079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CE6DBE1-6FC6-480C-A159-077DEBD9F154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-50220" yWindow="1860" windowWidth="22875" windowHeight="18315" xr2:uid="{D878BE86-2F5F-0A4D-A519-F89662502C45}"/>
+    <workbookView xWindow="17670" yWindow="90" windowWidth="22755" windowHeight="20805" activeTab="1" xr2:uid="{D878BE86-2F5F-0A4D-A519-F89662502C45}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="54">
   <si>
     <t>Price</t>
   </si>
@@ -193,7 +193,13 @@
     <t>Maturity</t>
   </si>
   <si>
-    <t>Share</t>
+    <t>Delta</t>
+  </si>
+  <si>
+    <t>Current Price</t>
+  </si>
+  <si>
+    <t>Projected Price</t>
   </si>
 </sst>
 </file>
@@ -203,7 +209,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -255,6 +261,13 @@
       <color theme="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -360,11 +373,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -410,10 +424,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
@@ -948,7 +966,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F78BA437-81C4-AF4A-A9DD-BDF3BE4300E7}">
-  <dimension ref="A1:BD14"/>
+  <dimension ref="A1:BD16"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.125" style="10" bestFit="1" customWidth="1"/>
@@ -1550,11 +1568,28 @@
     </row>
     <row r="14" spans="1:56" x14ac:dyDescent="0.2">
       <c r="B14" s="10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C14" s="18">
         <f>+C11/Main!K3</f>
         <v>232.7828969246498</v>
+      </c>
+    </row>
+    <row r="15" spans="1:56" x14ac:dyDescent="0.2">
+      <c r="B15" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="11">
+        <v>32.56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:56" x14ac:dyDescent="0.2">
+      <c r="B16" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="29">
+        <f>(C14-C15)/C15</f>
+        <v>6.149351871150178</v>
       </c>
     </row>
   </sheetData>

--- a/VKTX.xlsx
+++ b/VKTX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6944C6CF-5CDC-4DEB-BEF3-728FF9E35079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD045522-3B27-4162-922C-2C0827847CBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-50220" yWindow="1860" windowWidth="22875" windowHeight="18315" xr2:uid="{D878BE86-2F5F-0A4D-A519-F89662502C45}"/>
+    <workbookView xWindow="7510" yWindow="2130" windowWidth="21940" windowHeight="16070" xr2:uid="{D878BE86-2F5F-0A4D-A519-F89662502C45}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="59">
   <si>
     <t>Price</t>
   </si>
@@ -130,9 +130,6 @@
     <t>Vomiting</t>
   </si>
   <si>
-    <t>Q423</t>
-  </si>
-  <si>
     <t>Phase III "SURMOUNT-1" - Mounjaro vs. placebo in obesity - NEJM 2022 - NCT04184622</t>
   </si>
   <si>
@@ -148,9 +145,6 @@
     <t>Molecule</t>
   </si>
   <si>
-    <t>Peptide</t>
-  </si>
-  <si>
     <t>Patents</t>
   </si>
   <si>
@@ -194,6 +188,33 @@
   </si>
   <si>
     <t>Share</t>
+  </si>
+  <si>
+    <t>peptidomimetic</t>
+  </si>
+  <si>
+    <t>7.5mg, 12.5mg, 17.5mg vs. placebo qw</t>
+  </si>
+  <si>
+    <t>Phase III "VANQUISH-2" n=1000 T2D/obesity - 78 week</t>
+  </si>
+  <si>
+    <t>Phase III "VANQUISH-1"</t>
+  </si>
+  <si>
+    <t>Enrollment completed 11/2025 - results in 2027</t>
+  </si>
+  <si>
+    <t>Q425</t>
+  </si>
+  <si>
+    <t>PIC</t>
+  </si>
+  <si>
+    <t>AD</t>
+  </si>
+  <si>
+    <t>LGND</t>
   </si>
 </sst>
 </file>
@@ -203,7 +224,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -216,23 +237,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -253,6 +257,14 @@
       <u/>
       <sz val="10"/>
       <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -362,34 +374,19 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -400,7 +397,7 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
@@ -410,6 +407,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -436,14 +441,14 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
       <xdr:colOff>368300</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>138793</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -813,135 +818,160 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{040B3CA5-3820-9A43-941C-559CF5F28934}">
-  <dimension ref="B2:L9"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="B2:L10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="10" customWidth="1"/>
-    <col min="2" max="3" width="11" style="10"/>
-    <col min="4" max="4" width="13" style="10" customWidth="1"/>
-    <col min="5" max="9" width="11" style="10"/>
-    <col min="10" max="10" width="8.25" style="10" customWidth="1"/>
-    <col min="11" max="12" width="8.375" style="10" customWidth="1"/>
-    <col min="13" max="16384" width="11" style="10"/>
+    <col min="1" max="1" width="3.33203125" style="1" customWidth="1"/>
+    <col min="2" max="3" width="11" style="1"/>
+    <col min="4" max="4" width="13" style="1" customWidth="1"/>
+    <col min="5" max="9" width="11" style="1"/>
+    <col min="10" max="10" width="8.25" style="1" customWidth="1"/>
+    <col min="11" max="12" width="8.33203125" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B2" s="20" t="s">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="23">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B3" s="24" t="s">
+      <c r="K2" s="14">
+        <v>34.92</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="25"/>
-      <c r="J3" s="10" t="s">
+      <c r="G3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H3" s="16"/>
+      <c r="J3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="10">
-        <f>100+4</f>
-        <v>104</v>
-      </c>
-      <c r="L3" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B4" s="24"/>
-      <c r="H4" s="25"/>
-      <c r="J4" s="10" t="s">
+      <c r="K3" s="6">
+        <v>115.554</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B4" s="15"/>
+      <c r="H4" s="16"/>
+      <c r="J4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K4" s="15">
+      <c r="K4" s="6">
         <f>+K2*K3</f>
-        <v>6656</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B5" s="24"/>
-      <c r="H5" s="25"/>
-      <c r="J5" s="10" t="s">
+        <v>4035.1456800000001</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B5" s="15"/>
+      <c r="H5" s="16"/>
+      <c r="J5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="K5" s="10">
-        <f>361+350</f>
-        <v>711</v>
-      </c>
-      <c r="L5" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B6" s="24"/>
-      <c r="H6" s="25"/>
-      <c r="J6" s="10" t="s">
+      <c r="K5" s="6">
+        <f>165.81+539.929</f>
+        <v>705.73900000000003</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B6" s="15"/>
+      <c r="H6" s="16"/>
+      <c r="J6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K6" s="10">
+      <c r="K6" s="1">
         <v>0</v>
       </c>
-      <c r="L6" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B7" s="24"/>
-      <c r="H7" s="25"/>
-      <c r="J7" s="10" t="s">
+      <c r="L6" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B7" s="15"/>
+      <c r="H7" s="16"/>
+      <c r="J7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K7" s="15">
+      <c r="K7" s="6">
         <f>+K4-K5+K6</f>
-        <v>5945</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B8" s="24"/>
-      <c r="H8" s="25"/>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B9" s="26"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="28"/>
+        <v>3329.4066800000001</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B8" s="15"/>
+      <c r="H8" s="16"/>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B9" s="17"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="19"/>
+      <c r="J9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K9" s="6">
+        <v>1486.229</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="J10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K10" s="6">
+        <v>847.54600000000005</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>55</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B3" location="'VK2735'!A1" display="VK2735" xr:uid="{4AD17D64-059A-4E16-BEBE-336A67CAA361}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -949,612 +979,612 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F78BA437-81C4-AF4A-A9DD-BDF3BE4300E7}">
   <dimension ref="A1:BD14"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="10.875" style="11"/>
-    <col min="6" max="16384" width="11" style="10"/>
+    <col min="1" max="1" width="5.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="10.83203125" style="2"/>
+    <col min="6" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:56" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:56" x14ac:dyDescent="0.2">
-      <c r="C2" s="11">
+    <row r="2" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="C2" s="2">
         <v>2024</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="2">
         <f>+C2+1</f>
         <v>2025</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="2">
         <f t="shared" ref="E2:Q2" si="0">+D2+1</f>
         <v>2026</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="1">
         <f t="shared" si="0"/>
         <v>2027</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="1">
         <f t="shared" si="0"/>
         <v>2028</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="1">
         <f t="shared" si="0"/>
         <v>2029</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="1">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
-      <c r="J2" s="10">
+      <c r="J2" s="1">
         <f t="shared" si="0"/>
         <v>2031</v>
       </c>
-      <c r="K2" s="10">
+      <c r="K2" s="1">
         <f t="shared" si="0"/>
         <v>2032</v>
       </c>
-      <c r="L2" s="10">
+      <c r="L2" s="1">
         <f t="shared" si="0"/>
         <v>2033</v>
       </c>
-      <c r="M2" s="10">
+      <c r="M2" s="1">
         <f t="shared" si="0"/>
         <v>2034</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="1">
         <f t="shared" si="0"/>
         <v>2035</v>
       </c>
-      <c r="O2" s="10">
+      <c r="O2" s="1">
         <f t="shared" si="0"/>
         <v>2036</v>
       </c>
-      <c r="P2" s="10">
+      <c r="P2" s="1">
         <f t="shared" si="0"/>
         <v>2037</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="Q2" s="1">
         <f t="shared" si="0"/>
         <v>2038</v>
       </c>
     </row>
-    <row r="3" spans="1:56" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="13" t="s">
+    <row r="3" spans="1:56" s="3" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="G3" s="14">
+      <c r="G3" s="5">
         <v>800</v>
       </c>
-      <c r="H3" s="14">
+      <c r="H3" s="5">
         <v>2500</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="5">
         <v>5500</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="5">
         <v>7000</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="5">
         <v>9000</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="5">
         <f>+K3*1.05</f>
         <v>9450</v>
       </c>
-      <c r="M3" s="14">
+      <c r="M3" s="5">
         <f t="shared" ref="M3:P3" si="1">+L3*1.05</f>
         <v>9922.5</v>
       </c>
-      <c r="N3" s="14">
+      <c r="N3" s="5">
         <f t="shared" si="1"/>
         <v>10418.625</v>
       </c>
-      <c r="O3" s="14">
+      <c r="O3" s="5">
         <f t="shared" si="1"/>
         <v>10939.55625</v>
       </c>
-      <c r="P3" s="14">
+      <c r="P3" s="5">
         <f t="shared" si="1"/>
         <v>11486.534062500001</v>
       </c>
     </row>
-    <row r="4" spans="1:56" x14ac:dyDescent="0.2">
-      <c r="B4" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" s="10">
+    <row r="4" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="1">
         <f>+G3*0.2</f>
         <v>160</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4" s="6">
         <f t="shared" ref="H4:J4" si="2">+H3*0.2</f>
         <v>500</v>
       </c>
-      <c r="I4" s="15">
+      <c r="I4" s="6">
         <f t="shared" si="2"/>
         <v>1100</v>
       </c>
-      <c r="J4" s="15">
+      <c r="J4" s="6">
         <f t="shared" si="2"/>
         <v>1400</v>
       </c>
-      <c r="K4" s="15">
+      <c r="K4" s="6">
         <f t="shared" ref="K4" si="3">+K3*0.2</f>
         <v>1800</v>
       </c>
-      <c r="L4" s="15">
+      <c r="L4" s="6">
         <f t="shared" ref="L4" si="4">+L3*0.2</f>
         <v>1890</v>
       </c>
-      <c r="M4" s="15">
+      <c r="M4" s="6">
         <f t="shared" ref="M4" si="5">+M3*0.2</f>
         <v>1984.5</v>
       </c>
-      <c r="N4" s="15">
+      <c r="N4" s="6">
         <f t="shared" ref="N4" si="6">+N3*0.2</f>
         <v>2083.7249999999999</v>
       </c>
-      <c r="O4" s="15">
+      <c r="O4" s="6">
         <f t="shared" ref="O4" si="7">+O3*0.2</f>
         <v>2187.9112500000001</v>
       </c>
-      <c r="P4" s="15">
+      <c r="P4" s="6">
         <f t="shared" ref="P4" si="8">+P3*0.2</f>
         <v>2297.3068125000004</v>
       </c>
     </row>
-    <row r="5" spans="1:56" x14ac:dyDescent="0.2">
-      <c r="B5" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" s="15">
+    <row r="5" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="6">
         <f>+G3-G4</f>
         <v>640</v>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="6">
         <f t="shared" ref="H5:J5" si="9">+H3-H4</f>
         <v>2000</v>
       </c>
-      <c r="I5" s="15">
+      <c r="I5" s="6">
         <f t="shared" si="9"/>
         <v>4400</v>
       </c>
-      <c r="J5" s="15">
+      <c r="J5" s="6">
         <f t="shared" si="9"/>
         <v>5600</v>
       </c>
-      <c r="K5" s="15">
+      <c r="K5" s="6">
         <f t="shared" ref="K5" si="10">+K3-K4</f>
         <v>7200</v>
       </c>
-      <c r="L5" s="15">
+      <c r="L5" s="6">
         <f t="shared" ref="L5" si="11">+L3-L4</f>
         <v>7560</v>
       </c>
-      <c r="M5" s="15">
+      <c r="M5" s="6">
         <f t="shared" ref="M5" si="12">+M3-M4</f>
         <v>7938</v>
       </c>
-      <c r="N5" s="15">
+      <c r="N5" s="6">
         <f t="shared" ref="N5" si="13">+N3-N4</f>
         <v>8334.9</v>
       </c>
-      <c r="O5" s="15">
+      <c r="O5" s="6">
         <f t="shared" ref="O5" si="14">+O3-O4</f>
         <v>8751.6450000000004</v>
       </c>
-      <c r="P5" s="15">
+      <c r="P5" s="6">
         <f t="shared" ref="P5" si="15">+P3-P4</f>
         <v>9189.2272499999999</v>
       </c>
     </row>
-    <row r="6" spans="1:56" x14ac:dyDescent="0.2">
-      <c r="B6" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="G6" s="15">
+    <row r="6" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="6">
         <v>2000</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="6">
         <v>1500</v>
       </c>
-      <c r="I6" s="15">
+      <c r="I6" s="6">
         <v>1000</v>
       </c>
-      <c r="J6" s="15">
+      <c r="J6" s="6">
         <v>1000</v>
       </c>
-      <c r="K6" s="15">
+      <c r="K6" s="6">
         <v>1000</v>
       </c>
-      <c r="L6" s="15">
+      <c r="L6" s="6">
         <v>1000</v>
       </c>
-      <c r="M6" s="15">
+      <c r="M6" s="6">
         <v>1000</v>
       </c>
-      <c r="N6" s="15">
+      <c r="N6" s="6">
         <v>1000</v>
       </c>
-      <c r="O6" s="15">
+      <c r="O6" s="6">
         <v>1000</v>
       </c>
-      <c r="P6" s="15">
+      <c r="P6" s="6">
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:56" x14ac:dyDescent="0.2">
-      <c r="B7" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="10">
+    <row r="7" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="1">
         <v>-500</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="1">
         <v>-500</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="1">
         <v>-500</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="1">
         <v>-500</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="6">
         <f>+G5-G6</f>
         <v>-1360</v>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="6">
         <f t="shared" ref="H7:P7" si="16">+H5-H6</f>
         <v>500</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="6">
         <f t="shared" si="16"/>
         <v>3400</v>
       </c>
-      <c r="J7" s="15">
+      <c r="J7" s="6">
         <f t="shared" si="16"/>
         <v>4600</v>
       </c>
-      <c r="K7" s="15">
+      <c r="K7" s="6">
         <f t="shared" si="16"/>
         <v>6200</v>
       </c>
-      <c r="L7" s="15">
+      <c r="L7" s="6">
         <f t="shared" si="16"/>
         <v>6560</v>
       </c>
-      <c r="M7" s="15">
+      <c r="M7" s="6">
         <f t="shared" si="16"/>
         <v>6938</v>
       </c>
-      <c r="N7" s="15">
+      <c r="N7" s="6">
         <f t="shared" si="16"/>
         <v>7334.9</v>
       </c>
-      <c r="O7" s="15">
+      <c r="O7" s="6">
         <f t="shared" si="16"/>
         <v>7751.6450000000004</v>
       </c>
-      <c r="P7" s="15">
+      <c r="P7" s="6">
         <f t="shared" si="16"/>
         <v>8189.2272499999999</v>
       </c>
     </row>
-    <row r="8" spans="1:56" x14ac:dyDescent="0.2">
-      <c r="B8" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15">
+    <row r="8" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6">
         <v>0</v>
       </c>
-      <c r="I8" s="15">
+      <c r="I8" s="6">
         <f>+I7*0.1</f>
         <v>340</v>
       </c>
-      <c r="J8" s="15">
+      <c r="J8" s="6">
         <f>+J7*0.2</f>
         <v>920</v>
       </c>
-      <c r="K8" s="15">
+      <c r="K8" s="6">
         <f t="shared" ref="K8:P8" si="17">+K7*0.2</f>
         <v>1240</v>
       </c>
-      <c r="L8" s="15">
+      <c r="L8" s="6">
         <f t="shared" si="17"/>
         <v>1312</v>
       </c>
-      <c r="M8" s="15">
+      <c r="M8" s="6">
         <f t="shared" si="17"/>
         <v>1387.6000000000001</v>
       </c>
-      <c r="N8" s="15">
+      <c r="N8" s="6">
         <f t="shared" si="17"/>
         <v>1466.98</v>
       </c>
-      <c r="O8" s="15">
+      <c r="O8" s="6">
         <f t="shared" si="17"/>
         <v>1550.3290000000002</v>
       </c>
-      <c r="P8" s="15">
+      <c r="P8" s="6">
         <f t="shared" si="17"/>
         <v>1637.84545</v>
       </c>
     </row>
-    <row r="9" spans="1:56" x14ac:dyDescent="0.2">
-      <c r="B9" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="16">
+    <row r="9" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="B9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="7">
         <f>+C7-C8</f>
         <v>-500</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="7">
         <f t="shared" ref="D9:P9" si="18">+D7-D8</f>
         <v>-500</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="7">
         <f t="shared" si="18"/>
         <v>-500</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="7">
         <f t="shared" si="18"/>
         <v>-500</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="7">
         <f t="shared" si="18"/>
         <v>-1360</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="7">
         <f t="shared" si="18"/>
         <v>500</v>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="7">
         <f t="shared" si="18"/>
         <v>3060</v>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="7">
         <f t="shared" si="18"/>
         <v>3680</v>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="7">
         <f t="shared" si="18"/>
         <v>4960</v>
       </c>
-      <c r="L9" s="16">
+      <c r="L9" s="7">
         <f t="shared" si="18"/>
         <v>5248</v>
       </c>
-      <c r="M9" s="16">
+      <c r="M9" s="7">
         <f t="shared" si="18"/>
         <v>5550.4</v>
       </c>
-      <c r="N9" s="16">
+      <c r="N9" s="7">
         <f t="shared" si="18"/>
         <v>5867.92</v>
       </c>
-      <c r="O9" s="16">
+      <c r="O9" s="7">
         <f t="shared" si="18"/>
         <v>6201.3160000000007</v>
       </c>
-      <c r="P9" s="16">
+      <c r="P9" s="7">
         <f t="shared" si="18"/>
         <v>6551.3818000000001</v>
       </c>
-      <c r="Q9" s="16">
+      <c r="Q9" s="7">
         <f>+P9*(1+$C$13)</f>
         <v>6223.8127100000002</v>
       </c>
-      <c r="R9" s="16">
+      <c r="R9" s="7">
         <f t="shared" ref="R9:BD9" si="19">+Q9*(1+$C$13)</f>
         <v>5912.6220745000001</v>
       </c>
-      <c r="S9" s="16">
+      <c r="S9" s="7">
         <f t="shared" si="19"/>
         <v>5616.9909707749994</v>
       </c>
-      <c r="T9" s="16">
+      <c r="T9" s="7">
         <f t="shared" si="19"/>
         <v>5336.1414222362491</v>
       </c>
-      <c r="U9" s="16">
+      <c r="U9" s="7">
         <f t="shared" si="19"/>
         <v>5069.3343511244366</v>
       </c>
-      <c r="V9" s="16">
+      <c r="V9" s="7">
         <f t="shared" si="19"/>
         <v>4815.8676335682148</v>
       </c>
-      <c r="W9" s="16">
+      <c r="W9" s="7">
         <f t="shared" si="19"/>
         <v>4575.0742518898041</v>
       </c>
-      <c r="X9" s="16">
+      <c r="X9" s="7">
         <f t="shared" si="19"/>
         <v>4346.3205392953141</v>
       </c>
-      <c r="Y9" s="16">
+      <c r="Y9" s="7">
         <f t="shared" si="19"/>
         <v>4129.0045123305481</v>
       </c>
-      <c r="Z9" s="16">
+      <c r="Z9" s="7">
         <f t="shared" si="19"/>
         <v>3922.5542867140207</v>
       </c>
-      <c r="AA9" s="16">
+      <c r="AA9" s="7">
         <f t="shared" si="19"/>
         <v>3726.4265723783196</v>
       </c>
-      <c r="AB9" s="16">
+      <c r="AB9" s="7">
         <f t="shared" si="19"/>
         <v>3540.1052437594035</v>
       </c>
-      <c r="AC9" s="16">
+      <c r="AC9" s="7">
         <f t="shared" si="19"/>
         <v>3363.0999815714331</v>
       </c>
-      <c r="AD9" s="16">
+      <c r="AD9" s="7">
         <f t="shared" si="19"/>
         <v>3194.9449824928611</v>
       </c>
-      <c r="AE9" s="16">
+      <c r="AE9" s="7">
         <f t="shared" si="19"/>
         <v>3035.197733368218</v>
       </c>
-      <c r="AF9" s="16">
+      <c r="AF9" s="7">
         <f t="shared" si="19"/>
         <v>2883.4378466998069</v>
       </c>
-      <c r="AG9" s="16">
+      <c r="AG9" s="7">
         <f t="shared" si="19"/>
         <v>2739.2659543648165</v>
       </c>
-      <c r="AH9" s="16">
+      <c r="AH9" s="7">
         <f t="shared" si="19"/>
         <v>2602.3026566465755</v>
       </c>
-      <c r="AI9" s="16">
+      <c r="AI9" s="7">
         <f t="shared" si="19"/>
         <v>2472.1875238142466</v>
       </c>
-      <c r="AJ9" s="16">
+      <c r="AJ9" s="7">
         <f t="shared" si="19"/>
         <v>2348.5781476235343</v>
       </c>
-      <c r="AK9" s="16">
+      <c r="AK9" s="7">
         <f t="shared" si="19"/>
         <v>2231.1492402423573</v>
       </c>
-      <c r="AL9" s="16">
+      <c r="AL9" s="7">
         <f t="shared" si="19"/>
         <v>2119.5917782302395</v>
       </c>
-      <c r="AM9" s="16">
+      <c r="AM9" s="7">
         <f t="shared" si="19"/>
         <v>2013.6121893187274</v>
       </c>
-      <c r="AN9" s="16">
+      <c r="AN9" s="7">
         <f t="shared" si="19"/>
         <v>1912.9315798527909</v>
       </c>
-      <c r="AO9" s="16">
+      <c r="AO9" s="7">
         <f t="shared" si="19"/>
         <v>1817.2850008601513</v>
       </c>
-      <c r="AP9" s="16">
+      <c r="AP9" s="7">
         <f t="shared" si="19"/>
         <v>1726.4207508171437</v>
       </c>
-      <c r="AQ9" s="16">
+      <c r="AQ9" s="7">
         <f t="shared" si="19"/>
         <v>1640.0997132762864</v>
       </c>
-      <c r="AR9" s="16">
+      <c r="AR9" s="7">
         <f t="shared" si="19"/>
         <v>1558.0947276124721</v>
       </c>
-      <c r="AS9" s="16">
+      <c r="AS9" s="7">
         <f t="shared" si="19"/>
         <v>1480.1899912318484</v>
       </c>
-      <c r="AT9" s="16">
+      <c r="AT9" s="7">
         <f t="shared" si="19"/>
         <v>1406.1804916702558</v>
       </c>
-      <c r="AU9" s="16">
+      <c r="AU9" s="7">
         <f t="shared" si="19"/>
         <v>1335.871467086743</v>
       </c>
-      <c r="AV9" s="16">
+      <c r="AV9" s="7">
         <f t="shared" si="19"/>
         <v>1269.0778937324058</v>
       </c>
-      <c r="AW9" s="16">
+      <c r="AW9" s="7">
         <f t="shared" si="19"/>
         <v>1205.6239990457855</v>
       </c>
-      <c r="AX9" s="16">
+      <c r="AX9" s="7">
         <f t="shared" si="19"/>
         <v>1145.3427990934961</v>
       </c>
-      <c r="AY9" s="16">
+      <c r="AY9" s="7">
         <f t="shared" si="19"/>
         <v>1088.0756591388213</v>
       </c>
-      <c r="AZ9" s="16">
+      <c r="AZ9" s="7">
         <f t="shared" si="19"/>
         <v>1033.6718761818802</v>
       </c>
-      <c r="BA9" s="16">
+      <c r="BA9" s="7">
         <f t="shared" si="19"/>
         <v>981.9882823727861</v>
       </c>
-      <c r="BB9" s="16">
+      <c r="BB9" s="7">
         <f t="shared" si="19"/>
         <v>932.8888682541467</v>
       </c>
-      <c r="BC9" s="16">
+      <c r="BC9" s="7">
         <f t="shared" si="19"/>
         <v>886.24442484143935</v>
       </c>
-      <c r="BD9" s="16">
+      <c r="BD9" s="7">
         <f t="shared" si="19"/>
         <v>841.93220359936731</v>
       </c>
     </row>
-    <row r="11" spans="1:56" x14ac:dyDescent="0.2">
-      <c r="B11" s="10" t="s">
+    <row r="11" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="7">
+        <f>NPV(C12,C9:DP9)+Main!K5-Main!K6</f>
+        <v>24204.160280163582</v>
+      </c>
+    </row>
+    <row r="12" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="B12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="8">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="16">
-        <f>NPV(C12,C9:DP9)+Main!K5-Main!K6</f>
-        <v>24209.42128016358</v>
-      </c>
-    </row>
-    <row r="12" spans="1:56" x14ac:dyDescent="0.2">
-      <c r="B12" s="10" t="s">
+      <c r="C13" s="8">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="14" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="17">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:56" x14ac:dyDescent="0.2">
-      <c r="B13" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="17">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="14" spans="1:56" x14ac:dyDescent="0.2">
-      <c r="B14" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="18">
+      <c r="C14" s="9">
         <f>+C11/Main!K3</f>
-        <v>232.7828969246498</v>
+        <v>209.46189902697944</v>
       </c>
     </row>
   </sheetData>
@@ -1567,219 +1597,240 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BF3D612-CA62-7245-A7A4-8AA6A7D65875}">
-  <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F31"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="8">
+      <c r="C4" s="21">
         <v>11744873</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C6" s="2" t="s">
+    <row r="6" spans="1:6" ht="13" x14ac:dyDescent="0.3">
+      <c r="C6" s="22" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C7" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="13" x14ac:dyDescent="0.3">
+      <c r="C9" s="22" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C10" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="13" x14ac:dyDescent="0.3">
+      <c r="C12" s="22" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D7" s="3" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F13" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C8" t="s">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D8">
+      <c r="D14" s="1">
         <v>-1.8</v>
       </c>
-      <c r="E8" s="4">
-        <f t="shared" ref="E8:E11" si="0">+D8*2.2</f>
+      <c r="E14" s="23">
+        <f t="shared" ref="E14:E17" si="0">+D14*2.2</f>
         <v>-3.9600000000000004</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F14" s="24">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C9" t="s">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C15" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D9">
+      <c r="D15" s="1">
         <v>-9.1999999999999993</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E15" s="23">
         <f t="shared" si="0"/>
         <v>-20.239999999999998</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F15" s="24">
         <v>0.09</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C10" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D10">
+      <c r="D16" s="1">
         <v>-10.7</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E16" s="23">
         <f t="shared" si="0"/>
         <v>-23.54</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F16" s="24">
         <v>0.17</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C11" t="s">
+    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D11">
+      <c r="D17" s="1">
         <v>-13.3</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E17" s="23">
         <f t="shared" si="0"/>
         <v>-29.260000000000005</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F17" s="24">
         <v>0.17</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C12" s="1" t="s">
+    <row r="18" spans="3:6" ht="13" x14ac:dyDescent="0.3">
+      <c r="C18" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D18" s="3">
         <v>-14.6</v>
       </c>
-      <c r="E12" s="5">
-        <f>+D12*2.2</f>
+      <c r="E18" s="25">
+        <f>+D18*2.2</f>
         <v>-32.120000000000005</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F18" s="24">
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C14" t="s">
+    <row r="20" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C20" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D20" s="24">
         <v>0.43</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E20" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C15" t="s">
+    <row r="21" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C21" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D21" s="24">
         <v>0.18</v>
       </c>
     </row>
-    <row r="19" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C19" s="2" t="s">
+    <row r="25" spans="3:6" ht="13" x14ac:dyDescent="0.3">
+      <c r="C25" s="22" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D26" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="20" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D20" s="3" t="s">
+      <c r="E26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="3:6" ht="13" x14ac:dyDescent="0.3">
+      <c r="C27" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C21" t="s">
+      <c r="D27" s="4">
+        <v>-12.8</v>
+      </c>
+    </row>
+    <row r="28" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C28" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="2">
+        <v>-2.7</v>
+      </c>
+    </row>
+    <row r="29" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C29" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="7">
-        <v>-12.8</v>
-      </c>
-    </row>
-    <row r="22" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C22" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="3">
-        <v>-2.7</v>
-      </c>
-    </row>
-    <row r="23" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C23" t="s">
-        <v>34</v>
-      </c>
-      <c r="E23" s="6">
+      <c r="E29" s="24">
         <v>0.25</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F29" s="24">
         <v>0.08</v>
       </c>
     </row>
-    <row r="24" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C24" t="s">
+    <row r="30" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C30" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E30" s="24">
         <v>0.33</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F30" s="24">
         <v>0.11</v>
       </c>
     </row>
-    <row r="25" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C25" t="s">
+    <row r="31" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C31" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E31" s="24">
         <v>0.31</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F31" s="24">
         <v>0.12</v>
       </c>
     </row>
